--- a/output/Data and Chart Outputs/taiwan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/taiwan_power_generation_daily.xlsx
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>951.4638</v>
+        <v>951.4639</v>
       </c>
     </row>
     <row r="3">
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1014.1028</v>
+        <v>1014.1029</v>
       </c>
     </row>
     <row r="4">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1181.1796</v>
+        <v>1181.1798</v>
       </c>
     </row>
   </sheetData>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8046.4</v>
+        <v>8047.2</v>
       </c>
       <c r="J19" t="n">
-        <v>24936</v>
+        <v>24935.2</v>
       </c>
       <c r="K19" t="n">
         <v>8157.9</v>
@@ -1934,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>10067.9</v>
+        <v>10128.8</v>
       </c>
       <c r="J25" t="n">
-        <v>22398.3</v>
+        <v>22337.5</v>
       </c>
       <c r="K25" t="n">
         <v>9391.700000000001</v>
@@ -2045,10 +2045,10 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6685.9</v>
+        <v>6689.2</v>
       </c>
       <c r="J28" t="n">
-        <v>32672</v>
+        <v>32668.7</v>
       </c>
       <c r="K28" t="n">
         <v>6056</v>
@@ -2563,10 +2563,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>6781.2</v>
+        <v>6829.2</v>
       </c>
       <c r="J42" t="n">
-        <v>21496.6</v>
+        <v>21448.6</v>
       </c>
       <c r="K42" t="n">
         <v>7869.6</v>
@@ -3081,10 +3081,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3355.2</v>
+        <v>3358.5</v>
       </c>
       <c r="J56" t="n">
-        <v>37942.9</v>
+        <v>37939.6</v>
       </c>
       <c r="K56" t="n">
         <v>7201.1</v>
@@ -3192,10 +3192,10 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3358.1</v>
+        <v>3374.2</v>
       </c>
       <c r="J59" t="n">
-        <v>39145</v>
+        <v>39128.9</v>
       </c>
       <c r="K59" t="n">
         <v>6772.6</v>
@@ -3229,10 +3229,10 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>5992.6</v>
+        <v>6011.7</v>
       </c>
       <c r="J60" t="n">
-        <v>40218.4</v>
+        <v>40199.4</v>
       </c>
       <c r="K60" t="n">
         <v>6854.2</v>
@@ -4043,10 +4043,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>5687.1</v>
+        <v>5692.6</v>
       </c>
       <c r="J82" t="n">
-        <v>39409.3</v>
+        <v>39403.8</v>
       </c>
       <c r="K82" t="n">
         <v>6626.7</v>
@@ -4302,10 +4302,10 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>6918.6</v>
+        <v>7071.8</v>
       </c>
       <c r="J89" t="n">
-        <v>37635</v>
+        <v>37481.9</v>
       </c>
       <c r="K89" t="n">
         <v>6829.1</v>
@@ -4339,10 +4339,10 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>11037.9</v>
+        <v>11194</v>
       </c>
       <c r="J90" t="n">
-        <v>36804.9</v>
+        <v>36648.9</v>
       </c>
       <c r="K90" t="n">
         <v>10103.7</v>
@@ -4473,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4521,6 +4521,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>2026-05-31T23:50:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mapping_version</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4668,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other_MWh</t>
+          <t>Oil_MWh</t>
         </is>
       </c>
     </row>
